--- a/test-data/downloaded.xlsx
+++ b/test-data/downloaded.xlsx
@@ -37,7 +37,7 @@
     <t>Summer</t>
   </si>
   <si>
-    <t>Sapota yirb2s</t>
+    <t>Sapota s4ylwl</t>
   </si>
   <si>
     <t>Red</t>

--- a/test-data/downloaded.xlsx
+++ b/test-data/downloaded.xlsx
@@ -37,7 +37,7 @@
     <t>Summer</t>
   </si>
   <si>
-    <t>Sapota s4ylwl</t>
+    <t>Sapota msxz91</t>
   </si>
   <si>
     <t>Red</t>
